--- a/code/src/Q1/outputs/表1_问题1调度结果.xlsx
+++ b/code/src/Q1/outputs/表1_问题1调度结果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhurunjie\Desktop\51\code\src\Q1\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBB4BEC-63CE-49B4-9D91-44660A3AE26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE06A02-CD25-4312-83B7-1A2B1DC92EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="880" windowWidth="20140" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="1630" windowWidth="20140" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表1_调度明细" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="27">
   <si>
     <t>序号</t>
   </si>
@@ -47,22 +47,40 @@
     <t>00:03:20</t>
   </si>
   <si>
-    <t>01:33:20</t>
+    <t>00:21:20</t>
   </si>
   <si>
     <t>A1</t>
   </si>
   <si>
+    <t>精密灌装机1-2</t>
+  </si>
+  <si>
+    <t>精密灌装机1-3</t>
+  </si>
+  <si>
+    <t>精密灌装机1-4</t>
+  </si>
+  <si>
+    <t>精密灌装机1-5</t>
+  </si>
+  <si>
     <t>自动化输送臂1-1</t>
   </si>
   <si>
-    <t>01:15:20</t>
+    <t>自动化输送臂1-2</t>
+  </si>
+  <si>
+    <t>自动化输送臂1-3</t>
+  </si>
+  <si>
+    <t>自动化输送臂1-4</t>
   </si>
   <si>
     <t>高速抛光机1-1</t>
   </si>
   <si>
-    <t>06:33:20</t>
+    <t>05:21:20</t>
   </si>
   <si>
     <t>A2</t>
@@ -71,13 +89,13 @@
     <t>工业清洗机1-1</t>
   </si>
   <si>
-    <t>03:33:20</t>
+    <t>02:21:20</t>
   </si>
   <si>
     <t>自动传感多功能机1-1</t>
   </si>
   <si>
-    <t>11:33:20</t>
+    <t>10:21:20</t>
   </si>
   <si>
     <t>A3</t>
@@ -454,12 +472,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="41.08984375" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" customWidth="1"/>
-    <col min="5" max="5" width="32.7265625" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" customWidth="1"/>
+    <col min="4" max="4" width="26.08984375" customWidth="1"/>
+    <col min="5" max="5" width="20.08984375" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -496,7 +516,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>5400</v>
+        <v>1080</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -513,10 +533,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>4320</v>
+        <v>1080</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -527,19 +547,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>18000</v>
+        <v>1080</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,19 +567,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>7200</v>
+        <v>1080</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -567,19 +587,159 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>1080</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>1080</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>1080</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>1080</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>1080</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="E6">
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11">
         <v>18000</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <v>7200</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
         <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13">
+        <v>18000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -595,12 +755,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>41600</v>
+        <v>37280</v>
       </c>
     </row>
   </sheetData>
